--- a/excell/past_symposia.xlsx
+++ b/excell/past_symposia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MWSCAS Web Site\2026-08 MWSCAS Web Site\MWSCAS_GitHub_Beta5\Past Symposia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBB9214-CBFD-4655-A0A5-CE91927FE03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AAD0B16-F468-4C73-832D-9CBCCEC5F8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,12 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="351">
   <si>
     <t>Era</t>
   </si>
@@ -166,9 +167,6 @@
     <t>Spring 1966</t>
   </si>
   <si>
-    <t>W.A. Blackwell</t>
-  </si>
-  <si>
     <t>10th</t>
   </si>
   <si>
@@ -211,9 +209,6 @@
     <t>Spring 1969</t>
   </si>
   <si>
-    <t>A.J. Aggarwal</t>
-  </si>
-  <si>
     <t>13th</t>
   </si>
   <si>
@@ -226,9 +221,6 @@
     <t>Spring 1970</t>
   </si>
   <si>
-    <t>B.A. Shenoi</t>
-  </si>
-  <si>
     <t>14th</t>
   </si>
   <si>
@@ -268,9 +260,6 @@
     <t>April 8-11, 1973</t>
   </si>
   <si>
-    <t>P.H. Roe</t>
-  </si>
-  <si>
     <t>17th</t>
   </si>
   <si>
@@ -298,9 +287,6 @@
     <t>Aug. 11-12, 1975</t>
   </si>
   <si>
-    <t>M.N.S. Swamy</t>
-  </si>
-  <si>
     <t>19th</t>
   </si>
   <si>
@@ -328,9 +314,6 @@
     <t>Aug. 15-17, 1977</t>
   </si>
   <si>
-    <t>R. Saeks and K.S. Chao</t>
-  </si>
-  <si>
     <t>21st</t>
   </si>
   <si>
@@ -343,9 +326,6 @@
     <t>Aug. 15-17, 1978</t>
   </si>
   <si>
-    <t>H.W. Hale and A.N. Michel</t>
-  </si>
-  <si>
     <t>22nd</t>
   </si>
   <si>
@@ -391,9 +371,6 @@
     <t>June 29-30, 1981</t>
   </si>
   <si>
-    <t>S. Karni and P. Dorato</t>
-  </si>
-  <si>
     <t>25th</t>
   </si>
   <si>
@@ -526,9 +503,6 @@
     <t>Aug. 12-15, 1990</t>
   </si>
   <si>
-    <t>R.H. Johnston</t>
-  </si>
-  <si>
     <t>34th</t>
   </si>
   <si>
@@ -601,9 +575,6 @@
     <t>Aug. 13-16, 1995</t>
   </si>
   <si>
-    <t>L.P. Caloba</t>
-  </si>
-  <si>
     <t>39th</t>
   </si>
   <si>
@@ -979,9 +950,6 @@
     <t>August 9–11, 2021</t>
   </si>
   <si>
-    <t>Information being verified</t>
-  </si>
-  <si>
     <t>65th</t>
   </si>
   <si>
@@ -1042,9 +1010,6 @@
     <t>Soumyajit Mandal; Rashmi Jha</t>
   </si>
   <si>
-    <t>(If you know, please email soderstrand@ieee.org)</t>
-  </si>
-  <si>
     <t>Mac Van Valkenburg</t>
   </si>
   <si>
@@ -1052,6 +1017,63 @@
   </si>
   <si>
     <t xml:space="preserve">Colorado State Univ. Ft. Collins, CO </t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>Past MWSCAS Symposia</t>
+  </si>
+  <si>
+    <t>Neeraj Magotra and Randy Geiger</t>
+  </si>
+  <si>
+    <t>Pamela Abshire and Jennifer Blain</t>
+  </si>
+  <si>
+    <t>Vasily Moshnyaga and Hidetoshi Onodera</t>
+  </si>
+  <si>
+    <t>Fathi M Salem</t>
+  </si>
+  <si>
+    <t>This webpage presents the history of MWSCAS and lists all of the confernces from its beginnings in 1955 until the present.  The list of conferences is divided into three eras:  (1) Foundational (1955-1979), (2) Growth (1980-1999) and (3) Modern (2000 to present).  If you wish to skip the history and go directly to the list of past symposia, just click one of the buttons below:</t>
+  </si>
+  <si>
+    <t>James D. Graham</t>
+  </si>
+  <si>
+    <t>William A. Blackwell</t>
+  </si>
+  <si>
+    <t>Jake K. Aggarwal</t>
+  </si>
+  <si>
+    <t>Belle A. Shenoi</t>
+  </si>
+  <si>
+    <t>Peter Hugh O'Neil Roe (P.H. O'N Roe)</t>
+  </si>
+  <si>
+    <t>M.N.S. Swamy (M.N. Srikanta Swamy)</t>
+  </si>
+  <si>
+    <t>Richard (Dick) Saeks and Kwong S. Chao</t>
+  </si>
+  <si>
+    <t>Shlomo Karni and Peter Dorato</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> R.H. Johnston (Ronald H. Johnston)</t>
+  </si>
+  <si>
+    <t>Luiz Pereira Calôba</t>
+  </si>
+  <si>
+    <t>Harry W. Hale and Anthony N. Michel</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.90625" customWidth="1"/>
@@ -1402,63 +1424,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+        <v>332</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
+        <v>334</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1466,19 +1464,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1486,19 +1484,19 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>340</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1506,19 +1504,19 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>341</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1526,19 +1524,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1546,19 +1544,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1566,19 +1564,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1586,19 +1584,19 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1606,19 +1604,19 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1626,19 +1624,19 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1646,19 +1644,19 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1666,19 +1664,19 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1686,19 +1684,19 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1706,19 +1704,19 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1726,19 +1724,19 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1746,19 +1744,19 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1766,19 +1764,19 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>92</v>
+        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1786,19 +1784,19 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1806,19 +1804,19 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>102</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1826,19 +1824,19 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1846,959 +1844,999 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>112</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F24" t="s">
-        <v>118</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F25" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F26" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" t="s">
         <v>113</v>
       </c>
-      <c r="B27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C27" t="s">
-        <v>130</v>
-      </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="F27" t="s">
-        <v>133</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F28" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F30" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F32" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="E33" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="F33" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="E34" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F34" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="F35" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="D36" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="E36" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="F36" t="s">
-        <v>178</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D37" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="F37" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C38" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="F38" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D39" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="E39" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="F39" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="E40" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="F40" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B41" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="C41" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="E41" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="F41" t="s">
-        <v>202</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="C43" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D43" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E43" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="F43" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="B44" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C44" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="D44" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="F44" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C45" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="E45" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="F45" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="C46" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="E46" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="F46" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>203</v>
+      </c>
+      <c r="B47" t="s">
+        <v>209</v>
+      </c>
+      <c r="C47" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47" t="s">
         <v>213</v>
-      </c>
-      <c r="B47" t="s">
-        <v>229</v>
-      </c>
-      <c r="C47" t="s">
-        <v>230</v>
-      </c>
-      <c r="D47" t="s">
-        <v>231</v>
-      </c>
-      <c r="E47" t="s">
-        <v>232</v>
-      </c>
-      <c r="F47" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="C48" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="D48" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="E48" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="F48" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B49" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="C49" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="D49" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="E49" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="F49" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B50" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="C50" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="D50" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="E50" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="F50" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B51" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="C51" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="D51" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="E51" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="F51" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B52" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="C52" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="D52" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E52" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="F52" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B53" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="C53" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D53" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="E53" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="F53" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B54" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="C54" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D54" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E54" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F54" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B55" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C55" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="D55" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="E55" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="F55" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B56" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="C56" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="D56" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="E56" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="F56" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B57" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D57" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="E57" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="F57" t="s">
-        <v>282</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C58" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>342</v>
+        <v>265</v>
       </c>
       <c r="E58" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F58" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B59" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="C59" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="D59" t="s">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="E59" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="F59" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B60" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="C60" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="D60" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="E60" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="F60" t="s">
-        <v>148</v>
+        <v>276</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B61" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="C61" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D61" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="E61" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="F61" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B62" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="C62" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="D62" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="E62" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="F62" t="s">
-        <v>304</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="C63" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="D63" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="E63" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="F63" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B64" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="C64" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="D64" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="E64" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="F64" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="C65" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="D65" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="E65" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="F65" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B66" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C66" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="D66" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="E66" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="F66" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B67" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="C67" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="E67" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="F67" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B68" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="C68" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="D68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E68" t="s">
         <v>312</v>
       </c>
-      <c r="E68" t="s">
-        <v>330</v>
-      </c>
       <c r="F68" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B69" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="C69" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="D69" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E69" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="F69" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B70" t="s">
+        <v>317</v>
+      </c>
+      <c r="C70" t="s">
+        <v>318</v>
+      </c>
+      <c r="D70" t="s">
+        <v>302</v>
+      </c>
+      <c r="E70" t="s">
+        <v>319</v>
+      </c>
+      <c r="F70" t="s">
         <v>335</v>
       </c>
-      <c r="C70" t="s">
-        <v>336</v>
-      </c>
-      <c r="D70" t="s">
-        <v>337</v>
-      </c>
-      <c r="E70" t="s">
-        <v>338</v>
-      </c>
-      <c r="F70" t="s">
-        <v>339</v>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" t="s">
+        <v>320</v>
+      </c>
+      <c r="C71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D71" t="s">
+        <v>307</v>
+      </c>
+      <c r="E71" t="s">
+        <v>322</v>
+      </c>
+      <c r="F71" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>203</v>
+      </c>
+      <c r="B72" t="s">
+        <v>324</v>
+      </c>
+      <c r="C72" t="s">
+        <v>325</v>
+      </c>
+      <c r="D72" t="s">
+        <v>326</v>
+      </c>
+      <c r="E72" t="s">
+        <v>327</v>
+      </c>
+      <c r="F72" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
